--- a/output/pdf_financials_xlsx/CM.xlsx
+++ b/output/pdf_financials_xlsx/CM.xlsx
@@ -790,22 +790,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0</v>
+        <v>782</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0</v>
+        <v>804</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0</v>
+        <v>822</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>853</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0</v>
+        <v>823</v>
       </c>
     </row>
     <row r="16">
@@ -11263,7 +11263,11 @@
           <t>Occupancy costs</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E158" s="5" t="n">
         <v>782</v>
       </c>
